--- a/samples/planted-mistakes.xlsx
+++ b/samples/planted-mistakes.xlsx
@@ -924,7 +924,7 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>44</v>
@@ -1190,7 +1190,7 @@
         <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
         <v>38</v>
